--- a/Resultat/deltakere_kategorisert.xlsx
+++ b/Resultat/deltakere_kategorisert.xlsx
@@ -441,540 +441,540 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26834</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Malin Johnerud Schau</t>
+          <t>Aleksander Åshovd-Larsen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Renate Flatøy</t>
+          <t>Anders Johansen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>26257</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Per Martin Solli</t>
+          <t>Andreas Gjetåsaune</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22263</t>
+          <t>25107</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jan Cato Sparby</t>
+          <t>Arnt Myrhaug</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jan Helge Johnsen</t>
+          <t>Beate Johnerud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22815</t>
+          <t>26036</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pål Sigurd Romskaug</t>
+          <t>Bjørg Ester Eriksen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Øyvind Harang</t>
+          <t>Bjørnar Sandberg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jenny Mathiesen</t>
+          <t>Christer Aker</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27783</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jesper Hammelow-Berg Skjelland</t>
+          <t>Emilie Marie Aas</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>John Fossum</t>
+          <t>Espen Lund</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Øyvind Artvåg</t>
+          <t>Frank Havn</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jørgen Engdal</t>
+          <t>Geir Ståle Kristiansen</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Geir Ståle Kristiansen</t>
+          <t>Gina Larsen</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22074</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jørn Ryeng</t>
+          <t>Grethe Danielsen</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nils Holmgren</t>
+          <t>Grethe Walstad Fosseide</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>22263</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Morten Berntsen</t>
+          <t>Jan Cato Sparby</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mikkel B. Berntsen</t>
+          <t>Jan Helge Johnsen</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kjetil Myrstad</t>
+          <t>Jenny Mathiesen</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26952</t>
+          <t>27783</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mia Linnea Lillegjære</t>
+          <t>Jesper Hammelow-Berg Skjelland</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lars Herstadhagen</t>
+          <t>John Fossum</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>27823</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lars Tomren Støring</t>
+          <t>Jonny André Østli</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27823</t>
+          <t>27486</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jonny André Østli</t>
+          <t>Jørgen Engdal</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Roger Lindstad</t>
+          <t>Jørn Ryeng</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Klas Hallström Norström</t>
+          <t>Kjetil Myrstad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Anders Johansen</t>
+          <t>Klas Hallström Norström</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frank Havn</t>
+          <t>Lars Herstadhagen</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Beate Johnerud</t>
+          <t>Lars Tomren Støring</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>27194</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grethe Danielsen</t>
+          <t>Lena Haram Mittet</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gina Larsen</t>
+          <t>Lene Monica Aas Lillegjære</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aleksander Åshovd-Larsen</t>
+          <t>Magnus Haram Mittet</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trygve Fredriksen</t>
+          <t>Malin Johnerud Schau</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Andreas Gjetåsaune</t>
+          <t>Mathias Danielsen Otting</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trond Martin Thorbjørnsen</t>
+          <t>May Hege Lien</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>26952</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lena Haram Mittet</t>
+          <t>Mia Linnea Lillegjære</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magnus Haram Mittet</t>
+          <t>Mikkel B. Berntsen</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lene Monica Aas Lillegjære</t>
+          <t>Morten Berntsen</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>28329</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grethe Walstad Fosseide</t>
+          <t>Nils Holmgren</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28494</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tomas Morken Horvli</t>
+          <t>Per Martin Solli</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>25107</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Arnt Myrhaug</t>
+          <t>Pål Sigurd Romskaug</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bjørnar Sandberg</t>
+          <t>Renate Flatøy</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thor Morten Bjørge</t>
+          <t>Roger Lindstad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Christer Aker</t>
+          <t>Stian Hoff</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Stian Hoff</t>
+          <t>Thor Morten Bjørge</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Emilie Marie Aas</t>
+          <t>Tomas Morken Horvli</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Espen Lund</t>
+          <t>Tone Enoksen</t>
         </is>
       </c>
     </row>
@@ -993,48 +993,48 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28341</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tone Enoksen</t>
+          <t>Trond Martin Thorbjørnsen</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mathias Danielsen Otting</t>
+          <t>Trygve Fredriksen</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>26760</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>May Hege Lien</t>
+          <t>Øyvind Artvåg</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26036</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bjørg Ester Eriksen</t>
+          <t>Øyvind Harang</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thor Brattaker</t>
+          <t>Alfhild Danielsen</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1109,12 +1109,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Åge Malmo</t>
+          <t>Arnt Inge Kjesbu</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1126,12 +1126,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26680</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gisle Skjervø</t>
+          <t>Bård Jenssen</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Signar T Berger</t>
+          <t>Christian Pascal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22831</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Frank Tangen</t>
+          <t>Egil Toftaker</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Christian Pascal</t>
+          <t>Frank Tangen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Marit Lillebudal</t>
+          <t>Fredrikke Bøe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rigmor Skavhaug</t>
+          <t>Gisle Skjervø</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Reidar Stokkan Aas</t>
+          <t>Hallgeir Johansen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ronald Georgsen</t>
+          <t>Ingar Gabrielsen</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26931</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alfhild Danielsen</t>
+          <t>Jan Ivar Sparby</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Olav Ludvig Haabrekke</t>
+          <t>John Rune Johansen</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1296,12 +1296,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rune Mittet</t>
+          <t>Jon Kilsti</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marit Kilsti</t>
+          <t>Kjell Martin Johannessen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rolf Johan Boysen</t>
+          <t>Kjerstin Simarud Solbakken</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1347,12 +1347,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vidar Rise</t>
+          <t>Magnar Dyrnes</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1364,12 +1364,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>27273</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stein Roger Holdal</t>
+          <t>Marit Kilsti</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ingar Gabrielsen</t>
+          <t>Marit Lillebudal</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1398,12 +1398,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kjerstin Simarud Solbakken</t>
+          <t>Olav Ludvig Haabrekke</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bård Jenssen</t>
+          <t>Reidar Stokkan Aas</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arnt Inge Kjesbu</t>
+          <t>Rigmor Skavhaug</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1449,12 +1449,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>John Rune Johansen</t>
+          <t>Rolf Johan Boysen</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1466,12 +1466,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fredrikke Bøe</t>
+          <t>Ronald Georgsen</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hallgeir Johansen</t>
+          <t>Rune Mittet</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Magnar Dyrnes</t>
+          <t>Signar T Berger</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1517,12 +1517,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kjell Martin Johannessen</t>
+          <t>Stein Roger Holdal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Egil Toftaker</t>
+          <t>Thor Brattaker</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25167</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jon Kilsti</t>
+          <t>Vidar Rise</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jan Ivar Sparby</t>
+          <t>Åge Malmo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27562</t>
+          <t>27070</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Julian Solem</t>
+          <t>Christian Danielsen Otting</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1602,12 +1602,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>27070</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Christian Danielsen Otting</t>
+          <t>Evald Slaggerud Sandberg</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>27562</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Evald Slaggerud Sandberg</t>
+          <t>Julian Solem</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Per-Einar Walstad</t>
+          <t>Arne Gjetåsaune</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Marianne Lundstrøm</t>
+          <t>Birger Wibe</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1704,12 +1704,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rolf Erik Nyseter</t>
+          <t>Bjørn Richard Tangen</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Stein Roger Granum</t>
+          <t>Frank Robert Johansen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bjørn Richard Tangen</t>
+          <t>Frode Søreng</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Øyvind Skoglund</t>
+          <t>Jan Morten Hogstad</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -1772,12 +1772,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>22430</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Viggo Boneng</t>
+          <t>Marianne Lundstrøm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -1789,12 +1789,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>21069</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Birger Wibe</t>
+          <t>Ove Osgjelten</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -1806,12 +1806,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ove Osgjelten</t>
+          <t>Per Frode Sterud</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -1823,12 +1823,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Frank Robert Johansen</t>
+          <t>Per-Einar Walstad</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Arne Gjetåsaune</t>
+          <t>Rolf Erik Nyseter</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -1857,12 +1857,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jan Morten Hogstad</t>
+          <t>Stein Roger Granum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -1874,12 +1874,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Frode Søreng</t>
+          <t>Viggo Boneng</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -1908,12 +1908,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Per Frode Sterud</t>
+          <t>Øyvind Skoglund</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
